--- a/src/CJMSS.DataMigration/Migration Data Files/Zone_For_Dataverse.xlsx
+++ b/src/CJMSS.DataMigration/Migration Data Files/Zone_For_Dataverse.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yorgoinc.sharepoint.com/sites/PurpleDigitsProjects/Shared Documents/Jewelry Management System - JMS/Git/CJMSS/src/CJMSS.DataMigration/Migration Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_02332BDE7FBCB960BE8F97DCDC759B39BCD255F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E8A2895-4D64-4464-89DE-A7027F69413C}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_02332BDE7FBCB960BE8F97DCDC759B39BCD255F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272D8428-40A2-40F7-B0E3-065300308504}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Zones" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -638,6 +638,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2143,12 +2147,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8db5f02f-16cf-417c-b8d5-ebbf7ea068b2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a7dd6fdb-24d5-4f36-9343-ebf87e8a3b8a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2381,20 +2387,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8db5f02f-16cf-417c-b8d5-ebbf7ea068b2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a7dd6fdb-24d5-4f36-9343-ebf87e8a3b8a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94653BA8-E0FF-4D94-9A13-A5C960796A4D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8954F064-E7FE-4CAD-ABE6-DB0B4E7BE3A6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8db5f02f-16cf-417c-b8d5-ebbf7ea068b2"/>
+    <ds:schemaRef ds:uri="a7dd6fdb-24d5-4f36-9343-ebf87e8a3b8a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2419,12 +2426,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8954F064-E7FE-4CAD-ABE6-DB0B4E7BE3A6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94653BA8-E0FF-4D94-9A13-A5C960796A4D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8db5f02f-16cf-417c-b8d5-ebbf7ea068b2"/>
-    <ds:schemaRef ds:uri="a7dd6fdb-24d5-4f36-9343-ebf87e8a3b8a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>